--- a/desktop/templates/独秀账本-Excel导入模板.xlsx
+++ b/desktop/templates/独秀账本-Excel导入模板.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账单导入" sheetId="1" r:id="Rca4da93954994730"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R4481697ac6a34d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账单导入" sheetId="1" r:id="R9c34e723b13949f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R7a91232434114edf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,9 +14,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <x:numFmt numFmtId="201" formatCode="¥#,##0.00;[Red]-¥#,##0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -109,7 +110,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="51">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -214,6 +215,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -439,7 +452,8 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -455,7 +469,7 @@
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>从第 5 行开始填写。交易时间、收支、金额(元)为必填；请勿修改第 4 行表头。</x:v>
+        <x:v>从第 5 行开始填写。交易时间、收支、金额(元)为必填；订阅消费请填写订阅月数；请勿修改第 4 行表头。</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -484,6 +498,9 @@
         <x:v>分类</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
+        <x:v>订阅月数</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
         <x:v>备注</x:v>
       </x:c>
     </x:row>
@@ -506,7 +523,10 @@
       <x:c r="F5" s="26" t="str">
         <x:v>日常餐饮</x:v>
       </x:c>
-      <x:c r="G5" s="26" t="str">
+      <x:c r="G5" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
         <x:v>示例数据，可删除</x:v>
       </x:c>
     </x:row>
@@ -529,7 +549,10 @@
       <x:c r="F6" s="29" t="str">
         <x:v>交通出行</x:v>
       </x:c>
-      <x:c r="G6" s="29" t="str">
+      <x:c r="G6" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
         <x:v>示例数据，可删除</x:v>
       </x:c>
     </x:row>
@@ -552,7 +575,10 @@
       <x:c r="F7" s="29" t="str">
         <x:v>工资收入</x:v>
       </x:c>
-      <x:c r="G7" s="29" t="str">
+      <x:c r="G7" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
         <x:v>示例数据，可删除</x:v>
       </x:c>
     </x:row>
@@ -563,7 +589,8 @@
       <x:c r="D8" s="32"/>
       <x:c r="E8" s="32"/>
       <x:c r="F8" s="32"/>
-      <x:c r="G8" s="32"/>
+      <x:c r="G8" s="53"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="31"/>
@@ -572,7 +599,8 @@
       <x:c r="D9" s="32"/>
       <x:c r="E9" s="32"/>
       <x:c r="F9" s="32"/>
-      <x:c r="G9" s="32"/>
+      <x:c r="G9" s="53"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="31"/>
@@ -581,7 +609,8 @@
       <x:c r="D10" s="32"/>
       <x:c r="E10" s="32"/>
       <x:c r="F10" s="32"/>
-      <x:c r="G10" s="32"/>
+      <x:c r="G10" s="53"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="31"/>
@@ -590,7 +619,8 @@
       <x:c r="D11" s="32"/>
       <x:c r="E11" s="32"/>
       <x:c r="F11" s="32"/>
-      <x:c r="G11" s="32"/>
+      <x:c r="G11" s="53"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="31"/>
@@ -599,7 +629,8 @@
       <x:c r="D12" s="32"/>
       <x:c r="E12" s="32"/>
       <x:c r="F12" s="32"/>
-      <x:c r="G12" s="32"/>
+      <x:c r="G12" s="53"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="31"/>
@@ -608,7 +639,8 @@
       <x:c r="D13" s="32"/>
       <x:c r="E13" s="32"/>
       <x:c r="F13" s="32"/>
-      <x:c r="G13" s="32"/>
+      <x:c r="G13" s="53"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="31"/>
@@ -617,7 +649,8 @@
       <x:c r="D14" s="32"/>
       <x:c r="E14" s="32"/>
       <x:c r="F14" s="32"/>
-      <x:c r="G14" s="32"/>
+      <x:c r="G14" s="53"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="31"/>
@@ -626,7 +659,8 @@
       <x:c r="D15" s="32"/>
       <x:c r="E15" s="32"/>
       <x:c r="F15" s="32"/>
-      <x:c r="G15" s="32"/>
+      <x:c r="G15" s="53"/>
+      <x:c r="H15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="31"/>
@@ -635,7 +669,8 @@
       <x:c r="D16" s="32"/>
       <x:c r="E16" s="32"/>
       <x:c r="F16" s="32"/>
-      <x:c r="G16" s="32"/>
+      <x:c r="G16" s="53"/>
+      <x:c r="H16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="31"/>
@@ -644,7 +679,8 @@
       <x:c r="D17" s="32"/>
       <x:c r="E17" s="32"/>
       <x:c r="F17" s="32"/>
-      <x:c r="G17" s="32"/>
+      <x:c r="G17" s="53"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="31"/>
@@ -653,7 +689,8 @@
       <x:c r="D18" s="32"/>
       <x:c r="E18" s="32"/>
       <x:c r="F18" s="32"/>
-      <x:c r="G18" s="32"/>
+      <x:c r="G18" s="53"/>
+      <x:c r="H18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="31"/>
@@ -662,7 +699,8 @@
       <x:c r="D19" s="32"/>
       <x:c r="E19" s="32"/>
       <x:c r="F19" s="32"/>
-      <x:c r="G19" s="32"/>
+      <x:c r="G19" s="53"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="31"/>
@@ -671,7 +709,8 @@
       <x:c r="D20" s="32"/>
       <x:c r="E20" s="32"/>
       <x:c r="F20" s="32"/>
-      <x:c r="G20" s="32"/>
+      <x:c r="G20" s="53"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="31"/>
@@ -680,7 +719,8 @@
       <x:c r="D21" s="32"/>
       <x:c r="E21" s="32"/>
       <x:c r="F21" s="32"/>
-      <x:c r="G21" s="32"/>
+      <x:c r="G21" s="53"/>
+      <x:c r="H21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="31"/>
@@ -689,7 +729,8 @@
       <x:c r="D22" s="32"/>
       <x:c r="E22" s="32"/>
       <x:c r="F22" s="32"/>
-      <x:c r="G22" s="32"/>
+      <x:c r="G22" s="53"/>
+      <x:c r="H22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="31"/>
@@ -698,7 +739,8 @@
       <x:c r="D23" s="32"/>
       <x:c r="E23" s="32"/>
       <x:c r="F23" s="32"/>
-      <x:c r="G23" s="32"/>
+      <x:c r="G23" s="53"/>
+      <x:c r="H23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="31"/>
@@ -707,7 +749,8 @@
       <x:c r="D24" s="32"/>
       <x:c r="E24" s="32"/>
       <x:c r="F24" s="32"/>
-      <x:c r="G24" s="32"/>
+      <x:c r="G24" s="53"/>
+      <x:c r="H24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="31"/>
@@ -716,7 +759,8 @@
       <x:c r="D25" s="32"/>
       <x:c r="E25" s="32"/>
       <x:c r="F25" s="32"/>
-      <x:c r="G25" s="32"/>
+      <x:c r="G25" s="53"/>
+      <x:c r="H25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="31"/>
@@ -725,7 +769,8 @@
       <x:c r="D26" s="32"/>
       <x:c r="E26" s="32"/>
       <x:c r="F26" s="32"/>
-      <x:c r="G26" s="32"/>
+      <x:c r="G26" s="53"/>
+      <x:c r="H26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="31"/>
@@ -734,7 +779,8 @@
       <x:c r="D27" s="32"/>
       <x:c r="E27" s="32"/>
       <x:c r="F27" s="32"/>
-      <x:c r="G27" s="32"/>
+      <x:c r="G27" s="53"/>
+      <x:c r="H27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="31"/>
@@ -743,7 +789,8 @@
       <x:c r="D28" s="32"/>
       <x:c r="E28" s="32"/>
       <x:c r="F28" s="32"/>
-      <x:c r="G28" s="32"/>
+      <x:c r="G28" s="53"/>
+      <x:c r="H28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="31"/>
@@ -752,7 +799,8 @@
       <x:c r="D29" s="32"/>
       <x:c r="E29" s="32"/>
       <x:c r="F29" s="32"/>
-      <x:c r="G29" s="32"/>
+      <x:c r="G29" s="53"/>
+      <x:c r="H29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="31"/>
@@ -761,7 +809,8 @@
       <x:c r="D30" s="32"/>
       <x:c r="E30" s="32"/>
       <x:c r="F30" s="32"/>
-      <x:c r="G30" s="32"/>
+      <x:c r="G30" s="53"/>
+      <x:c r="H30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="31"/>
@@ -770,7 +819,8 @@
       <x:c r="D31" s="32"/>
       <x:c r="E31" s="32"/>
       <x:c r="F31" s="32"/>
-      <x:c r="G31" s="32"/>
+      <x:c r="G31" s="53"/>
+      <x:c r="H31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="31"/>
@@ -779,7 +829,8 @@
       <x:c r="D32" s="32"/>
       <x:c r="E32" s="32"/>
       <x:c r="F32" s="32"/>
-      <x:c r="G32" s="32"/>
+      <x:c r="G32" s="53"/>
+      <x:c r="H32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="31"/>
@@ -788,7 +839,8 @@
       <x:c r="D33" s="32"/>
       <x:c r="E33" s="32"/>
       <x:c r="F33" s="32"/>
-      <x:c r="G33" s="32"/>
+      <x:c r="G33" s="53"/>
+      <x:c r="H33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="31"/>
@@ -797,7 +849,8 @@
       <x:c r="D34" s="32"/>
       <x:c r="E34" s="32"/>
       <x:c r="F34" s="32"/>
-      <x:c r="G34" s="32"/>
+      <x:c r="G34" s="53"/>
+      <x:c r="H34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="31"/>
@@ -806,7 +859,8 @@
       <x:c r="D35" s="32"/>
       <x:c r="E35" s="32"/>
       <x:c r="F35" s="32"/>
-      <x:c r="G35" s="32"/>
+      <x:c r="G35" s="53"/>
+      <x:c r="H35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="31"/>
@@ -815,7 +869,8 @@
       <x:c r="D36" s="32"/>
       <x:c r="E36" s="32"/>
       <x:c r="F36" s="32"/>
-      <x:c r="G36" s="32"/>
+      <x:c r="G36" s="53"/>
+      <x:c r="H36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="31"/>
@@ -824,7 +879,8 @@
       <x:c r="D37" s="32"/>
       <x:c r="E37" s="32"/>
       <x:c r="F37" s="32"/>
-      <x:c r="G37" s="32"/>
+      <x:c r="G37" s="53"/>
+      <x:c r="H37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="31"/>
@@ -833,7 +889,8 @@
       <x:c r="D38" s="32"/>
       <x:c r="E38" s="32"/>
       <x:c r="F38" s="32"/>
-      <x:c r="G38" s="32"/>
+      <x:c r="G38" s="53"/>
+      <x:c r="H38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="31"/>
@@ -842,7 +899,8 @@
       <x:c r="D39" s="32"/>
       <x:c r="E39" s="32"/>
       <x:c r="F39" s="32"/>
-      <x:c r="G39" s="32"/>
+      <x:c r="G39" s="53"/>
+      <x:c r="H39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="31"/>
@@ -851,7 +909,8 @@
       <x:c r="D40" s="32"/>
       <x:c r="E40" s="32"/>
       <x:c r="F40" s="32"/>
-      <x:c r="G40" s="32"/>
+      <x:c r="G40" s="53"/>
+      <x:c r="H40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="31"/>
@@ -860,7 +919,8 @@
       <x:c r="D41" s="32"/>
       <x:c r="E41" s="32"/>
       <x:c r="F41" s="32"/>
-      <x:c r="G41" s="32"/>
+      <x:c r="G41" s="53"/>
+      <x:c r="H41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="31"/>
@@ -869,7 +929,8 @@
       <x:c r="D42" s="32"/>
       <x:c r="E42" s="32"/>
       <x:c r="F42" s="32"/>
-      <x:c r="G42" s="32"/>
+      <x:c r="G42" s="53"/>
+      <x:c r="H42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="31"/>
@@ -878,7 +939,8 @@
       <x:c r="D43" s="32"/>
       <x:c r="E43" s="32"/>
       <x:c r="F43" s="32"/>
-      <x:c r="G43" s="32"/>
+      <x:c r="G43" s="53"/>
+      <x:c r="H43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="31"/>
@@ -887,7 +949,8 @@
       <x:c r="D44" s="32"/>
       <x:c r="E44" s="32"/>
       <x:c r="F44" s="32"/>
-      <x:c r="G44" s="32"/>
+      <x:c r="G44" s="53"/>
+      <x:c r="H44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="31"/>
@@ -896,7 +959,8 @@
       <x:c r="D45" s="32"/>
       <x:c r="E45" s="32"/>
       <x:c r="F45" s="32"/>
-      <x:c r="G45" s="32"/>
+      <x:c r="G45" s="53"/>
+      <x:c r="H45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="31"/>
@@ -905,7 +969,8 @@
       <x:c r="D46" s="32"/>
       <x:c r="E46" s="32"/>
       <x:c r="F46" s="32"/>
-      <x:c r="G46" s="32"/>
+      <x:c r="G46" s="53"/>
+      <x:c r="H46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="31"/>
@@ -914,7 +979,8 @@
       <x:c r="D47" s="32"/>
       <x:c r="E47" s="32"/>
       <x:c r="F47" s="32"/>
-      <x:c r="G47" s="32"/>
+      <x:c r="G47" s="53"/>
+      <x:c r="H47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="31"/>
@@ -923,7 +989,8 @@
       <x:c r="D48" s="32"/>
       <x:c r="E48" s="32"/>
       <x:c r="F48" s="32"/>
-      <x:c r="G48" s="32"/>
+      <x:c r="G48" s="53"/>
+      <x:c r="H48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="31"/>
@@ -932,7 +999,8 @@
       <x:c r="D49" s="32"/>
       <x:c r="E49" s="32"/>
       <x:c r="F49" s="32"/>
-      <x:c r="G49" s="32"/>
+      <x:c r="G49" s="53"/>
+      <x:c r="H49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="31"/>
@@ -941,7 +1009,8 @@
       <x:c r="D50" s="32"/>
       <x:c r="E50" s="32"/>
       <x:c r="F50" s="32"/>
-      <x:c r="G50" s="32"/>
+      <x:c r="G50" s="53"/>
+      <x:c r="H50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="31"/>
@@ -950,7 +1019,8 @@
       <x:c r="D51" s="32"/>
       <x:c r="E51" s="32"/>
       <x:c r="F51" s="32"/>
-      <x:c r="G51" s="32"/>
+      <x:c r="G51" s="53"/>
+      <x:c r="H51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="31"/>
@@ -959,7 +1029,8 @@
       <x:c r="D52" s="32"/>
       <x:c r="E52" s="32"/>
       <x:c r="F52" s="32"/>
-      <x:c r="G52" s="32"/>
+      <x:c r="G52" s="53"/>
+      <x:c r="H52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="31"/>
@@ -968,7 +1039,8 @@
       <x:c r="D53" s="32"/>
       <x:c r="E53" s="32"/>
       <x:c r="F53" s="32"/>
-      <x:c r="G53" s="32"/>
+      <x:c r="G53" s="53"/>
+      <x:c r="H53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="31"/>
@@ -977,7 +1049,8 @@
       <x:c r="D54" s="32"/>
       <x:c r="E54" s="32"/>
       <x:c r="F54" s="32"/>
-      <x:c r="G54" s="32"/>
+      <x:c r="G54" s="53"/>
+      <x:c r="H54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="31"/>
@@ -986,7 +1059,8 @@
       <x:c r="D55" s="32"/>
       <x:c r="E55" s="32"/>
       <x:c r="F55" s="32"/>
-      <x:c r="G55" s="32"/>
+      <x:c r="G55" s="53"/>
+      <x:c r="H55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="31"/>
@@ -995,7 +1069,8 @@
       <x:c r="D56" s="32"/>
       <x:c r="E56" s="32"/>
       <x:c r="F56" s="32"/>
-      <x:c r="G56" s="32"/>
+      <x:c r="G56" s="53"/>
+      <x:c r="H56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="31"/>
@@ -1004,7 +1079,8 @@
       <x:c r="D57" s="32"/>
       <x:c r="E57" s="32"/>
       <x:c r="F57" s="32"/>
-      <x:c r="G57" s="32"/>
+      <x:c r="G57" s="53"/>
+      <x:c r="H57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="31"/>
@@ -1013,7 +1089,8 @@
       <x:c r="D58" s="32"/>
       <x:c r="E58" s="32"/>
       <x:c r="F58" s="32"/>
-      <x:c r="G58" s="32"/>
+      <x:c r="G58" s="53"/>
+      <x:c r="H58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="31"/>
@@ -1022,7 +1099,8 @@
       <x:c r="D59" s="32"/>
       <x:c r="E59" s="32"/>
       <x:c r="F59" s="32"/>
-      <x:c r="G59" s="32"/>
+      <x:c r="G59" s="53"/>
+      <x:c r="H59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="31"/>
@@ -1031,7 +1109,8 @@
       <x:c r="D60" s="32"/>
       <x:c r="E60" s="32"/>
       <x:c r="F60" s="32"/>
-      <x:c r="G60" s="32"/>
+      <x:c r="G60" s="53"/>
+      <x:c r="H60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="31"/>
@@ -1040,7 +1119,8 @@
       <x:c r="D61" s="32"/>
       <x:c r="E61" s="32"/>
       <x:c r="F61" s="32"/>
-      <x:c r="G61" s="32"/>
+      <x:c r="G61" s="53"/>
+      <x:c r="H61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="31"/>
@@ -1049,7 +1129,8 @@
       <x:c r="D62" s="32"/>
       <x:c r="E62" s="32"/>
       <x:c r="F62" s="32"/>
-      <x:c r="G62" s="32"/>
+      <x:c r="G62" s="53"/>
+      <x:c r="H62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="31"/>
@@ -1058,7 +1139,8 @@
       <x:c r="D63" s="32"/>
       <x:c r="E63" s="32"/>
       <x:c r="F63" s="32"/>
-      <x:c r="G63" s="32"/>
+      <x:c r="G63" s="53"/>
+      <x:c r="H63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="31"/>
@@ -1067,7 +1149,8 @@
       <x:c r="D64" s="32"/>
       <x:c r="E64" s="32"/>
       <x:c r="F64" s="32"/>
-      <x:c r="G64" s="32"/>
+      <x:c r="G64" s="53"/>
+      <x:c r="H64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="31"/>
@@ -1076,7 +1159,8 @@
       <x:c r="D65" s="32"/>
       <x:c r="E65" s="32"/>
       <x:c r="F65" s="32"/>
-      <x:c r="G65" s="32"/>
+      <x:c r="G65" s="53"/>
+      <x:c r="H65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="31"/>
@@ -1085,7 +1169,8 @@
       <x:c r="D66" s="32"/>
       <x:c r="E66" s="32"/>
       <x:c r="F66" s="32"/>
-      <x:c r="G66" s="32"/>
+      <x:c r="G66" s="53"/>
+      <x:c r="H66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="31"/>
@@ -1094,7 +1179,8 @@
       <x:c r="D67" s="32"/>
       <x:c r="E67" s="32"/>
       <x:c r="F67" s="32"/>
-      <x:c r="G67" s="32"/>
+      <x:c r="G67" s="53"/>
+      <x:c r="H67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="31"/>
@@ -1103,7 +1189,8 @@
       <x:c r="D68" s="32"/>
       <x:c r="E68" s="32"/>
       <x:c r="F68" s="32"/>
-      <x:c r="G68" s="32"/>
+      <x:c r="G68" s="53"/>
+      <x:c r="H68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="31"/>
@@ -1112,7 +1199,8 @@
       <x:c r="D69" s="32"/>
       <x:c r="E69" s="32"/>
       <x:c r="F69" s="32"/>
-      <x:c r="G69" s="32"/>
+      <x:c r="G69" s="53"/>
+      <x:c r="H69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="31"/>
@@ -1121,7 +1209,8 @@
       <x:c r="D70" s="32"/>
       <x:c r="E70" s="32"/>
       <x:c r="F70" s="32"/>
-      <x:c r="G70" s="32"/>
+      <x:c r="G70" s="53"/>
+      <x:c r="H70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="31"/>
@@ -1130,7 +1219,8 @@
       <x:c r="D71" s="32"/>
       <x:c r="E71" s="32"/>
       <x:c r="F71" s="32"/>
-      <x:c r="G71" s="32"/>
+      <x:c r="G71" s="53"/>
+      <x:c r="H71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="31"/>
@@ -1139,7 +1229,8 @@
       <x:c r="D72" s="32"/>
       <x:c r="E72" s="32"/>
       <x:c r="F72" s="32"/>
-      <x:c r="G72" s="32"/>
+      <x:c r="G72" s="53"/>
+      <x:c r="H72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="31"/>
@@ -1148,7 +1239,8 @@
       <x:c r="D73" s="32"/>
       <x:c r="E73" s="32"/>
       <x:c r="F73" s="32"/>
-      <x:c r="G73" s="32"/>
+      <x:c r="G73" s="53"/>
+      <x:c r="H73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="31"/>
@@ -1157,7 +1249,8 @@
       <x:c r="D74" s="32"/>
       <x:c r="E74" s="32"/>
       <x:c r="F74" s="32"/>
-      <x:c r="G74" s="32"/>
+      <x:c r="G74" s="53"/>
+      <x:c r="H74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="31"/>
@@ -1166,7 +1259,8 @@
       <x:c r="D75" s="32"/>
       <x:c r="E75" s="32"/>
       <x:c r="F75" s="32"/>
-      <x:c r="G75" s="32"/>
+      <x:c r="G75" s="53"/>
+      <x:c r="H75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="31"/>
@@ -1175,7 +1269,8 @@
       <x:c r="D76" s="32"/>
       <x:c r="E76" s="32"/>
       <x:c r="F76" s="32"/>
-      <x:c r="G76" s="32"/>
+      <x:c r="G76" s="53"/>
+      <x:c r="H76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="31"/>
@@ -1184,7 +1279,8 @@
       <x:c r="D77" s="32"/>
       <x:c r="E77" s="32"/>
       <x:c r="F77" s="32"/>
-      <x:c r="G77" s="32"/>
+      <x:c r="G77" s="53"/>
+      <x:c r="H77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="31"/>
@@ -1193,7 +1289,8 @@
       <x:c r="D78" s="32"/>
       <x:c r="E78" s="32"/>
       <x:c r="F78" s="32"/>
-      <x:c r="G78" s="32"/>
+      <x:c r="G78" s="53"/>
+      <x:c r="H78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="31"/>
@@ -1202,7 +1299,8 @@
       <x:c r="D79" s="32"/>
       <x:c r="E79" s="32"/>
       <x:c r="F79" s="32"/>
-      <x:c r="G79" s="32"/>
+      <x:c r="G79" s="53"/>
+      <x:c r="H79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="31"/>
@@ -1211,7 +1309,8 @@
       <x:c r="D80" s="32"/>
       <x:c r="E80" s="32"/>
       <x:c r="F80" s="32"/>
-      <x:c r="G80" s="32"/>
+      <x:c r="G80" s="53"/>
+      <x:c r="H80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="31"/>
@@ -1220,7 +1319,8 @@
       <x:c r="D81" s="32"/>
       <x:c r="E81" s="32"/>
       <x:c r="F81" s="32"/>
-      <x:c r="G81" s="32"/>
+      <x:c r="G81" s="53"/>
+      <x:c r="H81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="31"/>
@@ -1229,7 +1329,8 @@
       <x:c r="D82" s="32"/>
       <x:c r="E82" s="32"/>
       <x:c r="F82" s="32"/>
-      <x:c r="G82" s="32"/>
+      <x:c r="G82" s="53"/>
+      <x:c r="H82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="31"/>
@@ -1238,7 +1339,8 @@
       <x:c r="D83" s="32"/>
       <x:c r="E83" s="32"/>
       <x:c r="F83" s="32"/>
-      <x:c r="G83" s="32"/>
+      <x:c r="G83" s="53"/>
+      <x:c r="H83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="31"/>
@@ -1247,7 +1349,8 @@
       <x:c r="D84" s="32"/>
       <x:c r="E84" s="32"/>
       <x:c r="F84" s="32"/>
-      <x:c r="G84" s="32"/>
+      <x:c r="G84" s="53"/>
+      <x:c r="H84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="31"/>
@@ -1256,7 +1359,8 @@
       <x:c r="D85" s="32"/>
       <x:c r="E85" s="32"/>
       <x:c r="F85" s="32"/>
-      <x:c r="G85" s="32"/>
+      <x:c r="G85" s="53"/>
+      <x:c r="H85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="31"/>
@@ -1265,7 +1369,8 @@
       <x:c r="D86" s="32"/>
       <x:c r="E86" s="32"/>
       <x:c r="F86" s="32"/>
-      <x:c r="G86" s="32"/>
+      <x:c r="G86" s="53"/>
+      <x:c r="H86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="31"/>
@@ -1274,7 +1379,8 @@
       <x:c r="D87" s="32"/>
       <x:c r="E87" s="32"/>
       <x:c r="F87" s="32"/>
-      <x:c r="G87" s="32"/>
+      <x:c r="G87" s="53"/>
+      <x:c r="H87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="31"/>
@@ -1283,7 +1389,8 @@
       <x:c r="D88" s="32"/>
       <x:c r="E88" s="32"/>
       <x:c r="F88" s="32"/>
-      <x:c r="G88" s="32"/>
+      <x:c r="G88" s="53"/>
+      <x:c r="H88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="31"/>
@@ -1292,7 +1399,8 @@
       <x:c r="D89" s="32"/>
       <x:c r="E89" s="32"/>
       <x:c r="F89" s="32"/>
-      <x:c r="G89" s="32"/>
+      <x:c r="G89" s="53"/>
+      <x:c r="H89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="31"/>
@@ -1301,7 +1409,8 @@
       <x:c r="D90" s="32"/>
       <x:c r="E90" s="32"/>
       <x:c r="F90" s="32"/>
-      <x:c r="G90" s="32"/>
+      <x:c r="G90" s="53"/>
+      <x:c r="H90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="31"/>
@@ -1310,7 +1419,8 @@
       <x:c r="D91" s="32"/>
       <x:c r="E91" s="32"/>
       <x:c r="F91" s="32"/>
-      <x:c r="G91" s="32"/>
+      <x:c r="G91" s="53"/>
+      <x:c r="H91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="31"/>
@@ -1319,7 +1429,8 @@
       <x:c r="D92" s="32"/>
       <x:c r="E92" s="32"/>
       <x:c r="F92" s="32"/>
-      <x:c r="G92" s="32"/>
+      <x:c r="G92" s="53"/>
+      <x:c r="H92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="31"/>
@@ -1328,7 +1439,8 @@
       <x:c r="D93" s="32"/>
       <x:c r="E93" s="32"/>
       <x:c r="F93" s="32"/>
-      <x:c r="G93" s="32"/>
+      <x:c r="G93" s="53"/>
+      <x:c r="H93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="31"/>
@@ -1337,7 +1449,8 @@
       <x:c r="D94" s="32"/>
       <x:c r="E94" s="32"/>
       <x:c r="F94" s="32"/>
-      <x:c r="G94" s="32"/>
+      <x:c r="G94" s="53"/>
+      <x:c r="H94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="31"/>
@@ -1346,7 +1459,8 @@
       <x:c r="D95" s="32"/>
       <x:c r="E95" s="32"/>
       <x:c r="F95" s="32"/>
-      <x:c r="G95" s="32"/>
+      <x:c r="G95" s="53"/>
+      <x:c r="H95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="31"/>
@@ -1355,7 +1469,8 @@
       <x:c r="D96" s="32"/>
       <x:c r="E96" s="32"/>
       <x:c r="F96" s="32"/>
-      <x:c r="G96" s="32"/>
+      <x:c r="G96" s="53"/>
+      <x:c r="H96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="31"/>
@@ -1364,7 +1479,8 @@
       <x:c r="D97" s="32"/>
       <x:c r="E97" s="32"/>
       <x:c r="F97" s="32"/>
-      <x:c r="G97" s="32"/>
+      <x:c r="G97" s="53"/>
+      <x:c r="H97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="31"/>
@@ -1373,7 +1489,8 @@
       <x:c r="D98" s="32"/>
       <x:c r="E98" s="32"/>
       <x:c r="F98" s="32"/>
-      <x:c r="G98" s="32"/>
+      <x:c r="G98" s="53"/>
+      <x:c r="H98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="31"/>
@@ -1382,7 +1499,8 @@
       <x:c r="D99" s="32"/>
       <x:c r="E99" s="32"/>
       <x:c r="F99" s="32"/>
-      <x:c r="G99" s="32"/>
+      <x:c r="G99" s="53"/>
+      <x:c r="H99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="31"/>
@@ -1391,7 +1509,8 @@
       <x:c r="D100" s="32"/>
       <x:c r="E100" s="32"/>
       <x:c r="F100" s="32"/>
-      <x:c r="G100" s="32"/>
+      <x:c r="G100" s="53"/>
+      <x:c r="H100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="31"/>
@@ -1400,7 +1519,8 @@
       <x:c r="D101" s="32"/>
       <x:c r="E101" s="32"/>
       <x:c r="F101" s="32"/>
-      <x:c r="G101" s="32"/>
+      <x:c r="G101" s="53"/>
+      <x:c r="H101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="31"/>
@@ -1409,7 +1529,8 @@
       <x:c r="D102" s="32"/>
       <x:c r="E102" s="32"/>
       <x:c r="F102" s="32"/>
-      <x:c r="G102" s="32"/>
+      <x:c r="G102" s="53"/>
+      <x:c r="H102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="31"/>
@@ -1418,7 +1539,8 @@
       <x:c r="D103" s="32"/>
       <x:c r="E103" s="32"/>
       <x:c r="F103" s="32"/>
-      <x:c r="G103" s="32"/>
+      <x:c r="G103" s="53"/>
+      <x:c r="H103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="31"/>
@@ -1427,7 +1549,8 @@
       <x:c r="D104" s="32"/>
       <x:c r="E104" s="32"/>
       <x:c r="F104" s="32"/>
-      <x:c r="G104" s="32"/>
+      <x:c r="G104" s="53"/>
+      <x:c r="H104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="31"/>
@@ -1436,7 +1559,8 @@
       <x:c r="D105" s="32"/>
       <x:c r="E105" s="32"/>
       <x:c r="F105" s="32"/>
-      <x:c r="G105" s="32"/>
+      <x:c r="G105" s="53"/>
+      <x:c r="H105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="31"/>
@@ -1445,7 +1569,8 @@
       <x:c r="D106" s="32"/>
       <x:c r="E106" s="32"/>
       <x:c r="F106" s="32"/>
-      <x:c r="G106" s="32"/>
+      <x:c r="G106" s="53"/>
+      <x:c r="H106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="31"/>
@@ -1454,7 +1579,8 @@
       <x:c r="D107" s="32"/>
       <x:c r="E107" s="32"/>
       <x:c r="F107" s="32"/>
-      <x:c r="G107" s="32"/>
+      <x:c r="G107" s="53"/>
+      <x:c r="H107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="31"/>
@@ -1463,7 +1589,8 @@
       <x:c r="D108" s="32"/>
       <x:c r="E108" s="32"/>
       <x:c r="F108" s="32"/>
-      <x:c r="G108" s="32"/>
+      <x:c r="G108" s="53"/>
+      <x:c r="H108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="31"/>
@@ -1472,7 +1599,8 @@
       <x:c r="D109" s="32"/>
       <x:c r="E109" s="32"/>
       <x:c r="F109" s="32"/>
-      <x:c r="G109" s="32"/>
+      <x:c r="G109" s="53"/>
+      <x:c r="H109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="31"/>
@@ -1481,7 +1609,8 @@
       <x:c r="D110" s="32"/>
       <x:c r="E110" s="32"/>
       <x:c r="F110" s="32"/>
-      <x:c r="G110" s="32"/>
+      <x:c r="G110" s="53"/>
+      <x:c r="H110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="31"/>
@@ -1490,7 +1619,8 @@
       <x:c r="D111" s="32"/>
       <x:c r="E111" s="32"/>
       <x:c r="F111" s="32"/>
-      <x:c r="G111" s="32"/>
+      <x:c r="G111" s="53"/>
+      <x:c r="H111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="31"/>
@@ -1499,7 +1629,8 @@
       <x:c r="D112" s="32"/>
       <x:c r="E112" s="32"/>
       <x:c r="F112" s="32"/>
-      <x:c r="G112" s="32"/>
+      <x:c r="G112" s="53"/>
+      <x:c r="H112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="31"/>
@@ -1508,7 +1639,8 @@
       <x:c r="D113" s="32"/>
       <x:c r="E113" s="32"/>
       <x:c r="F113" s="32"/>
-      <x:c r="G113" s="32"/>
+      <x:c r="G113" s="53"/>
+      <x:c r="H113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="31"/>
@@ -1517,7 +1649,8 @@
       <x:c r="D114" s="32"/>
       <x:c r="E114" s="32"/>
       <x:c r="F114" s="32"/>
-      <x:c r="G114" s="32"/>
+      <x:c r="G114" s="53"/>
+      <x:c r="H114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="31"/>
@@ -1526,7 +1659,8 @@
       <x:c r="D115" s="32"/>
       <x:c r="E115" s="32"/>
       <x:c r="F115" s="32"/>
-      <x:c r="G115" s="32"/>
+      <x:c r="G115" s="53"/>
+      <x:c r="H115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="31"/>
@@ -1535,7 +1669,8 @@
       <x:c r="D116" s="32"/>
       <x:c r="E116" s="32"/>
       <x:c r="F116" s="32"/>
-      <x:c r="G116" s="32"/>
+      <x:c r="G116" s="53"/>
+      <x:c r="H116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="31"/>
@@ -1544,7 +1679,8 @@
       <x:c r="D117" s="32"/>
       <x:c r="E117" s="32"/>
       <x:c r="F117" s="32"/>
-      <x:c r="G117" s="32"/>
+      <x:c r="G117" s="53"/>
+      <x:c r="H117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="31"/>
@@ -1553,7 +1689,8 @@
       <x:c r="D118" s="32"/>
       <x:c r="E118" s="32"/>
       <x:c r="F118" s="32"/>
-      <x:c r="G118" s="32"/>
+      <x:c r="G118" s="53"/>
+      <x:c r="H118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="31"/>
@@ -1562,7 +1699,8 @@
       <x:c r="D119" s="32"/>
       <x:c r="E119" s="32"/>
       <x:c r="F119" s="32"/>
-      <x:c r="G119" s="32"/>
+      <x:c r="G119" s="53"/>
+      <x:c r="H119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="31"/>
@@ -1571,7 +1709,8 @@
       <x:c r="D120" s="32"/>
       <x:c r="E120" s="32"/>
       <x:c r="F120" s="32"/>
-      <x:c r="G120" s="32"/>
+      <x:c r="G120" s="53"/>
+      <x:c r="H120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="31"/>
@@ -1580,7 +1719,8 @@
       <x:c r="D121" s="32"/>
       <x:c r="E121" s="32"/>
       <x:c r="F121" s="32"/>
-      <x:c r="G121" s="32"/>
+      <x:c r="G121" s="53"/>
+      <x:c r="H121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="31"/>
@@ -1589,7 +1729,8 @@
       <x:c r="D122" s="32"/>
       <x:c r="E122" s="32"/>
       <x:c r="F122" s="32"/>
-      <x:c r="G122" s="32"/>
+      <x:c r="G122" s="53"/>
+      <x:c r="H122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="31"/>
@@ -1598,7 +1739,8 @@
       <x:c r="D123" s="32"/>
       <x:c r="E123" s="32"/>
       <x:c r="F123" s="32"/>
-      <x:c r="G123" s="32"/>
+      <x:c r="G123" s="53"/>
+      <x:c r="H123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="31"/>
@@ -1607,7 +1749,8 @@
       <x:c r="D124" s="32"/>
       <x:c r="E124" s="32"/>
       <x:c r="F124" s="32"/>
-      <x:c r="G124" s="32"/>
+      <x:c r="G124" s="53"/>
+      <x:c r="H124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="31"/>
@@ -1616,7 +1759,8 @@
       <x:c r="D125" s="32"/>
       <x:c r="E125" s="32"/>
       <x:c r="F125" s="32"/>
-      <x:c r="G125" s="32"/>
+      <x:c r="G125" s="53"/>
+      <x:c r="H125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="31"/>
@@ -1625,7 +1769,8 @@
       <x:c r="D126" s="32"/>
       <x:c r="E126" s="32"/>
       <x:c r="F126" s="32"/>
-      <x:c r="G126" s="32"/>
+      <x:c r="G126" s="53"/>
+      <x:c r="H126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="31"/>
@@ -1634,7 +1779,8 @@
       <x:c r="D127" s="32"/>
       <x:c r="E127" s="32"/>
       <x:c r="F127" s="32"/>
-      <x:c r="G127" s="32"/>
+      <x:c r="G127" s="53"/>
+      <x:c r="H127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="31"/>
@@ -1643,7 +1789,8 @@
       <x:c r="D128" s="32"/>
       <x:c r="E128" s="32"/>
       <x:c r="F128" s="32"/>
-      <x:c r="G128" s="32"/>
+      <x:c r="G128" s="53"/>
+      <x:c r="H128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="31"/>
@@ -1652,7 +1799,8 @@
       <x:c r="D129" s="32"/>
       <x:c r="E129" s="32"/>
       <x:c r="F129" s="32"/>
-      <x:c r="G129" s="32"/>
+      <x:c r="G129" s="53"/>
+      <x:c r="H129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="31"/>
@@ -1661,7 +1809,8 @@
       <x:c r="D130" s="32"/>
       <x:c r="E130" s="32"/>
       <x:c r="F130" s="32"/>
-      <x:c r="G130" s="32"/>
+      <x:c r="G130" s="53"/>
+      <x:c r="H130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="31"/>
@@ -1670,7 +1819,8 @@
       <x:c r="D131" s="32"/>
       <x:c r="E131" s="32"/>
       <x:c r="F131" s="32"/>
-      <x:c r="G131" s="32"/>
+      <x:c r="G131" s="53"/>
+      <x:c r="H131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="31"/>
@@ -1679,7 +1829,8 @@
       <x:c r="D132" s="32"/>
       <x:c r="E132" s="32"/>
       <x:c r="F132" s="32"/>
-      <x:c r="G132" s="32"/>
+      <x:c r="G132" s="53"/>
+      <x:c r="H132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="31"/>
@@ -1688,7 +1839,8 @@
       <x:c r="D133" s="32"/>
       <x:c r="E133" s="32"/>
       <x:c r="F133" s="32"/>
-      <x:c r="G133" s="32"/>
+      <x:c r="G133" s="53"/>
+      <x:c r="H133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="31"/>
@@ -1697,7 +1849,8 @@
       <x:c r="D134" s="32"/>
       <x:c r="E134" s="32"/>
       <x:c r="F134" s="32"/>
-      <x:c r="G134" s="32"/>
+      <x:c r="G134" s="53"/>
+      <x:c r="H134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="31"/>
@@ -1706,7 +1859,8 @@
       <x:c r="D135" s="32"/>
       <x:c r="E135" s="32"/>
       <x:c r="F135" s="32"/>
-      <x:c r="G135" s="32"/>
+      <x:c r="G135" s="53"/>
+      <x:c r="H135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="31"/>
@@ -1715,7 +1869,8 @@
       <x:c r="D136" s="32"/>
       <x:c r="E136" s="32"/>
       <x:c r="F136" s="32"/>
-      <x:c r="G136" s="32"/>
+      <x:c r="G136" s="53"/>
+      <x:c r="H136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="31"/>
@@ -1724,7 +1879,8 @@
       <x:c r="D137" s="32"/>
       <x:c r="E137" s="32"/>
       <x:c r="F137" s="32"/>
-      <x:c r="G137" s="32"/>
+      <x:c r="G137" s="53"/>
+      <x:c r="H137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="31"/>
@@ -1733,7 +1889,8 @@
       <x:c r="D138" s="32"/>
       <x:c r="E138" s="32"/>
       <x:c r="F138" s="32"/>
-      <x:c r="G138" s="32"/>
+      <x:c r="G138" s="53"/>
+      <x:c r="H138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="31"/>
@@ -1742,7 +1899,8 @@
       <x:c r="D139" s="32"/>
       <x:c r="E139" s="32"/>
       <x:c r="F139" s="32"/>
-      <x:c r="G139" s="32"/>
+      <x:c r="G139" s="53"/>
+      <x:c r="H139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="31"/>
@@ -1751,7 +1909,8 @@
       <x:c r="D140" s="32"/>
       <x:c r="E140" s="32"/>
       <x:c r="F140" s="32"/>
-      <x:c r="G140" s="32"/>
+      <x:c r="G140" s="53"/>
+      <x:c r="H140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="31"/>
@@ -1760,7 +1919,8 @@
       <x:c r="D141" s="32"/>
       <x:c r="E141" s="32"/>
       <x:c r="F141" s="32"/>
-      <x:c r="G141" s="32"/>
+      <x:c r="G141" s="53"/>
+      <x:c r="H141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="31"/>
@@ -1769,7 +1929,8 @@
       <x:c r="D142" s="32"/>
       <x:c r="E142" s="32"/>
       <x:c r="F142" s="32"/>
-      <x:c r="G142" s="32"/>
+      <x:c r="G142" s="53"/>
+      <x:c r="H142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="31"/>
@@ -1778,7 +1939,8 @@
       <x:c r="D143" s="32"/>
       <x:c r="E143" s="32"/>
       <x:c r="F143" s="32"/>
-      <x:c r="G143" s="32"/>
+      <x:c r="G143" s="53"/>
+      <x:c r="H143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="31"/>
@@ -1787,7 +1949,8 @@
       <x:c r="D144" s="32"/>
       <x:c r="E144" s="32"/>
       <x:c r="F144" s="32"/>
-      <x:c r="G144" s="32"/>
+      <x:c r="G144" s="53"/>
+      <x:c r="H144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="31"/>
@@ -1796,7 +1959,8 @@
       <x:c r="D145" s="32"/>
       <x:c r="E145" s="32"/>
       <x:c r="F145" s="32"/>
-      <x:c r="G145" s="32"/>
+      <x:c r="G145" s="53"/>
+      <x:c r="H145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="31"/>
@@ -1805,7 +1969,8 @@
       <x:c r="D146" s="32"/>
       <x:c r="E146" s="32"/>
       <x:c r="F146" s="32"/>
-      <x:c r="G146" s="32"/>
+      <x:c r="G146" s="53"/>
+      <x:c r="H146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="31"/>
@@ -1814,7 +1979,8 @@
       <x:c r="D147" s="32"/>
       <x:c r="E147" s="32"/>
       <x:c r="F147" s="32"/>
-      <x:c r="G147" s="32"/>
+      <x:c r="G147" s="53"/>
+      <x:c r="H147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="31"/>
@@ -1823,7 +1989,8 @@
       <x:c r="D148" s="32"/>
       <x:c r="E148" s="32"/>
       <x:c r="F148" s="32"/>
-      <x:c r="G148" s="32"/>
+      <x:c r="G148" s="53"/>
+      <x:c r="H148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="31"/>
@@ -1832,7 +1999,8 @@
       <x:c r="D149" s="32"/>
       <x:c r="E149" s="32"/>
       <x:c r="F149" s="32"/>
-      <x:c r="G149" s="32"/>
+      <x:c r="G149" s="53"/>
+      <x:c r="H149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="31"/>
@@ -1841,7 +2009,8 @@
       <x:c r="D150" s="32"/>
       <x:c r="E150" s="32"/>
       <x:c r="F150" s="32"/>
-      <x:c r="G150" s="32"/>
+      <x:c r="G150" s="53"/>
+      <x:c r="H150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="31"/>
@@ -1850,7 +2019,8 @@
       <x:c r="D151" s="32"/>
       <x:c r="E151" s="32"/>
       <x:c r="F151" s="32"/>
-      <x:c r="G151" s="32"/>
+      <x:c r="G151" s="53"/>
+      <x:c r="H151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="31"/>
@@ -1859,7 +2029,8 @@
       <x:c r="D152" s="32"/>
       <x:c r="E152" s="32"/>
       <x:c r="F152" s="32"/>
-      <x:c r="G152" s="32"/>
+      <x:c r="G152" s="53"/>
+      <x:c r="H152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="31"/>
@@ -1868,7 +2039,8 @@
       <x:c r="D153" s="32"/>
       <x:c r="E153" s="32"/>
       <x:c r="F153" s="32"/>
-      <x:c r="G153" s="32"/>
+      <x:c r="G153" s="53"/>
+      <x:c r="H153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="31"/>
@@ -1877,7 +2049,8 @@
       <x:c r="D154" s="32"/>
       <x:c r="E154" s="32"/>
       <x:c r="F154" s="32"/>
-      <x:c r="G154" s="32"/>
+      <x:c r="G154" s="53"/>
+      <x:c r="H154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="31"/>
@@ -1886,7 +2059,8 @@
       <x:c r="D155" s="32"/>
       <x:c r="E155" s="32"/>
       <x:c r="F155" s="32"/>
-      <x:c r="G155" s="32"/>
+      <x:c r="G155" s="53"/>
+      <x:c r="H155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="31"/>
@@ -1895,7 +2069,8 @@
       <x:c r="D156" s="32"/>
       <x:c r="E156" s="32"/>
       <x:c r="F156" s="32"/>
-      <x:c r="G156" s="32"/>
+      <x:c r="G156" s="53"/>
+      <x:c r="H156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="31"/>
@@ -1904,7 +2079,8 @@
       <x:c r="D157" s="32"/>
       <x:c r="E157" s="32"/>
       <x:c r="F157" s="32"/>
-      <x:c r="G157" s="32"/>
+      <x:c r="G157" s="53"/>
+      <x:c r="H157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="31"/>
@@ -1913,7 +2089,8 @@
       <x:c r="D158" s="32"/>
       <x:c r="E158" s="32"/>
       <x:c r="F158" s="32"/>
-      <x:c r="G158" s="32"/>
+      <x:c r="G158" s="53"/>
+      <x:c r="H158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="31"/>
@@ -1922,7 +2099,8 @@
       <x:c r="D159" s="32"/>
       <x:c r="E159" s="32"/>
       <x:c r="F159" s="32"/>
-      <x:c r="G159" s="32"/>
+      <x:c r="G159" s="53"/>
+      <x:c r="H159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="31"/>
@@ -1931,7 +2109,8 @@
       <x:c r="D160" s="32"/>
       <x:c r="E160" s="32"/>
       <x:c r="F160" s="32"/>
-      <x:c r="G160" s="32"/>
+      <x:c r="G160" s="53"/>
+      <x:c r="H160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="31"/>
@@ -1940,7 +2119,8 @@
       <x:c r="D161" s="32"/>
       <x:c r="E161" s="32"/>
       <x:c r="F161" s="32"/>
-      <x:c r="G161" s="32"/>
+      <x:c r="G161" s="53"/>
+      <x:c r="H161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="31"/>
@@ -1949,7 +2129,8 @@
       <x:c r="D162" s="32"/>
       <x:c r="E162" s="32"/>
       <x:c r="F162" s="32"/>
-      <x:c r="G162" s="32"/>
+      <x:c r="G162" s="53"/>
+      <x:c r="H162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="31"/>
@@ -1958,7 +2139,8 @@
       <x:c r="D163" s="32"/>
       <x:c r="E163" s="32"/>
       <x:c r="F163" s="32"/>
-      <x:c r="G163" s="32"/>
+      <x:c r="G163" s="53"/>
+      <x:c r="H163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="31"/>
@@ -1967,7 +2149,8 @@
       <x:c r="D164" s="32"/>
       <x:c r="E164" s="32"/>
       <x:c r="F164" s="32"/>
-      <x:c r="G164" s="32"/>
+      <x:c r="G164" s="53"/>
+      <x:c r="H164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="31"/>
@@ -1976,7 +2159,8 @@
       <x:c r="D165" s="32"/>
       <x:c r="E165" s="32"/>
       <x:c r="F165" s="32"/>
-      <x:c r="G165" s="32"/>
+      <x:c r="G165" s="53"/>
+      <x:c r="H165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="31"/>
@@ -1985,7 +2169,8 @@
       <x:c r="D166" s="32"/>
       <x:c r="E166" s="32"/>
       <x:c r="F166" s="32"/>
-      <x:c r="G166" s="32"/>
+      <x:c r="G166" s="53"/>
+      <x:c r="H166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="31"/>
@@ -1994,7 +2179,8 @@
       <x:c r="D167" s="32"/>
       <x:c r="E167" s="32"/>
       <x:c r="F167" s="32"/>
-      <x:c r="G167" s="32"/>
+      <x:c r="G167" s="53"/>
+      <x:c r="H167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="31"/>
@@ -2003,7 +2189,8 @@
       <x:c r="D168" s="32"/>
       <x:c r="E168" s="32"/>
       <x:c r="F168" s="32"/>
-      <x:c r="G168" s="32"/>
+      <x:c r="G168" s="53"/>
+      <x:c r="H168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="31"/>
@@ -2012,7 +2199,8 @@
       <x:c r="D169" s="32"/>
       <x:c r="E169" s="32"/>
       <x:c r="F169" s="32"/>
-      <x:c r="G169" s="32"/>
+      <x:c r="G169" s="53"/>
+      <x:c r="H169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="31"/>
@@ -2021,7 +2209,8 @@
       <x:c r="D170" s="32"/>
       <x:c r="E170" s="32"/>
       <x:c r="F170" s="32"/>
-      <x:c r="G170" s="32"/>
+      <x:c r="G170" s="53"/>
+      <x:c r="H170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="31"/>
@@ -2030,7 +2219,8 @@
       <x:c r="D171" s="32"/>
       <x:c r="E171" s="32"/>
       <x:c r="F171" s="32"/>
-      <x:c r="G171" s="32"/>
+      <x:c r="G171" s="53"/>
+      <x:c r="H171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="31"/>
@@ -2039,7 +2229,8 @@
       <x:c r="D172" s="32"/>
       <x:c r="E172" s="32"/>
       <x:c r="F172" s="32"/>
-      <x:c r="G172" s="32"/>
+      <x:c r="G172" s="53"/>
+      <x:c r="H172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="31"/>
@@ -2048,7 +2239,8 @@
       <x:c r="D173" s="32"/>
       <x:c r="E173" s="32"/>
       <x:c r="F173" s="32"/>
-      <x:c r="G173" s="32"/>
+      <x:c r="G173" s="53"/>
+      <x:c r="H173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="31"/>
@@ -2057,7 +2249,8 @@
       <x:c r="D174" s="32"/>
       <x:c r="E174" s="32"/>
       <x:c r="F174" s="32"/>
-      <x:c r="G174" s="32"/>
+      <x:c r="G174" s="53"/>
+      <x:c r="H174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="31"/>
@@ -2066,7 +2259,8 @@
       <x:c r="D175" s="32"/>
       <x:c r="E175" s="32"/>
       <x:c r="F175" s="32"/>
-      <x:c r="G175" s="32"/>
+      <x:c r="G175" s="53"/>
+      <x:c r="H175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="31"/>
@@ -2075,7 +2269,8 @@
       <x:c r="D176" s="32"/>
       <x:c r="E176" s="32"/>
       <x:c r="F176" s="32"/>
-      <x:c r="G176" s="32"/>
+      <x:c r="G176" s="53"/>
+      <x:c r="H176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="31"/>
@@ -2084,7 +2279,8 @@
       <x:c r="D177" s="32"/>
       <x:c r="E177" s="32"/>
       <x:c r="F177" s="32"/>
-      <x:c r="G177" s="32"/>
+      <x:c r="G177" s="53"/>
+      <x:c r="H177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="31"/>
@@ -2093,7 +2289,8 @@
       <x:c r="D178" s="32"/>
       <x:c r="E178" s="32"/>
       <x:c r="F178" s="32"/>
-      <x:c r="G178" s="32"/>
+      <x:c r="G178" s="53"/>
+      <x:c r="H178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="31"/>
@@ -2102,7 +2299,8 @@
       <x:c r="D179" s="32"/>
       <x:c r="E179" s="32"/>
       <x:c r="F179" s="32"/>
-      <x:c r="G179" s="32"/>
+      <x:c r="G179" s="53"/>
+      <x:c r="H179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="31"/>
@@ -2111,7 +2309,8 @@
       <x:c r="D180" s="32"/>
       <x:c r="E180" s="32"/>
       <x:c r="F180" s="32"/>
-      <x:c r="G180" s="32"/>
+      <x:c r="G180" s="53"/>
+      <x:c r="H180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="31"/>
@@ -2120,7 +2319,8 @@
       <x:c r="D181" s="32"/>
       <x:c r="E181" s="32"/>
       <x:c r="F181" s="32"/>
-      <x:c r="G181" s="32"/>
+      <x:c r="G181" s="53"/>
+      <x:c r="H181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="31"/>
@@ -2129,7 +2329,8 @@
       <x:c r="D182" s="32"/>
       <x:c r="E182" s="32"/>
       <x:c r="F182" s="32"/>
-      <x:c r="G182" s="32"/>
+      <x:c r="G182" s="53"/>
+      <x:c r="H182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="31"/>
@@ -2138,7 +2339,8 @@
       <x:c r="D183" s="32"/>
       <x:c r="E183" s="32"/>
       <x:c r="F183" s="32"/>
-      <x:c r="G183" s="32"/>
+      <x:c r="G183" s="53"/>
+      <x:c r="H183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="31"/>
@@ -2147,7 +2349,8 @@
       <x:c r="D184" s="32"/>
       <x:c r="E184" s="32"/>
       <x:c r="F184" s="32"/>
-      <x:c r="G184" s="32"/>
+      <x:c r="G184" s="53"/>
+      <x:c r="H184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="31"/>
@@ -2156,7 +2359,8 @@
       <x:c r="D185" s="32"/>
       <x:c r="E185" s="32"/>
       <x:c r="F185" s="32"/>
-      <x:c r="G185" s="32"/>
+      <x:c r="G185" s="53"/>
+      <x:c r="H185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="31"/>
@@ -2165,7 +2369,8 @@
       <x:c r="D186" s="32"/>
       <x:c r="E186" s="32"/>
       <x:c r="F186" s="32"/>
-      <x:c r="G186" s="32"/>
+      <x:c r="G186" s="53"/>
+      <x:c r="H186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="31"/>
@@ -2174,7 +2379,8 @@
       <x:c r="D187" s="32"/>
       <x:c r="E187" s="32"/>
       <x:c r="F187" s="32"/>
-      <x:c r="G187" s="32"/>
+      <x:c r="G187" s="53"/>
+      <x:c r="H187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="31"/>
@@ -2183,7 +2389,8 @@
       <x:c r="D188" s="32"/>
       <x:c r="E188" s="32"/>
       <x:c r="F188" s="32"/>
-      <x:c r="G188" s="32"/>
+      <x:c r="G188" s="53"/>
+      <x:c r="H188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="31"/>
@@ -2192,7 +2399,8 @@
       <x:c r="D189" s="32"/>
       <x:c r="E189" s="32"/>
       <x:c r="F189" s="32"/>
-      <x:c r="G189" s="32"/>
+      <x:c r="G189" s="53"/>
+      <x:c r="H189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="31"/>
@@ -2201,7 +2409,8 @@
       <x:c r="D190" s="32"/>
       <x:c r="E190" s="32"/>
       <x:c r="F190" s="32"/>
-      <x:c r="G190" s="32"/>
+      <x:c r="G190" s="53"/>
+      <x:c r="H190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="31"/>
@@ -2210,7 +2419,8 @@
       <x:c r="D191" s="32"/>
       <x:c r="E191" s="32"/>
       <x:c r="F191" s="32"/>
-      <x:c r="G191" s="32"/>
+      <x:c r="G191" s="53"/>
+      <x:c r="H191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="31"/>
@@ -2219,7 +2429,8 @@
       <x:c r="D192" s="32"/>
       <x:c r="E192" s="32"/>
       <x:c r="F192" s="32"/>
-      <x:c r="G192" s="32"/>
+      <x:c r="G192" s="53"/>
+      <x:c r="H192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="31"/>
@@ -2228,7 +2439,8 @@
       <x:c r="D193" s="32"/>
       <x:c r="E193" s="32"/>
       <x:c r="F193" s="32"/>
-      <x:c r="G193" s="32"/>
+      <x:c r="G193" s="53"/>
+      <x:c r="H193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="31"/>
@@ -2237,7 +2449,8 @@
       <x:c r="D194" s="32"/>
       <x:c r="E194" s="32"/>
       <x:c r="F194" s="32"/>
-      <x:c r="G194" s="32"/>
+      <x:c r="G194" s="53"/>
+      <x:c r="H194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="31"/>
@@ -2246,7 +2459,8 @@
       <x:c r="D195" s="32"/>
       <x:c r="E195" s="32"/>
       <x:c r="F195" s="32"/>
-      <x:c r="G195" s="32"/>
+      <x:c r="G195" s="53"/>
+      <x:c r="H195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="31"/>
@@ -2255,7 +2469,8 @@
       <x:c r="D196" s="32"/>
       <x:c r="E196" s="32"/>
       <x:c r="F196" s="32"/>
-      <x:c r="G196" s="32"/>
+      <x:c r="G196" s="53"/>
+      <x:c r="H196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="31"/>
@@ -2264,7 +2479,8 @@
       <x:c r="D197" s="32"/>
       <x:c r="E197" s="32"/>
       <x:c r="F197" s="32"/>
-      <x:c r="G197" s="32"/>
+      <x:c r="G197" s="53"/>
+      <x:c r="H197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="31"/>
@@ -2273,7 +2489,8 @@
       <x:c r="D198" s="32"/>
       <x:c r="E198" s="32"/>
       <x:c r="F198" s="32"/>
-      <x:c r="G198" s="32"/>
+      <x:c r="G198" s="53"/>
+      <x:c r="H198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="31"/>
@@ -2282,7 +2499,8 @@
       <x:c r="D199" s="32"/>
       <x:c r="E199" s="32"/>
       <x:c r="F199" s="32"/>
-      <x:c r="G199" s="32"/>
+      <x:c r="G199" s="53"/>
+      <x:c r="H199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="31"/>
@@ -2291,7 +2509,8 @@
       <x:c r="D200" s="32"/>
       <x:c r="E200" s="32"/>
       <x:c r="F200" s="32"/>
-      <x:c r="G200" s="32"/>
+      <x:c r="G200" s="53"/>
+      <x:c r="H200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="31"/>
@@ -2300,7 +2519,8 @@
       <x:c r="D201" s="32"/>
       <x:c r="E201" s="32"/>
       <x:c r="F201" s="32"/>
-      <x:c r="G201" s="32"/>
+      <x:c r="G201" s="53"/>
+      <x:c r="H201"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="31"/>
@@ -2309,7 +2529,8 @@
       <x:c r="D202" s="32"/>
       <x:c r="E202" s="32"/>
       <x:c r="F202" s="32"/>
-      <x:c r="G202" s="32"/>
+      <x:c r="G202" s="53"/>
+      <x:c r="H202"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="31"/>
@@ -2318,7 +2539,8 @@
       <x:c r="D203" s="32"/>
       <x:c r="E203" s="32"/>
       <x:c r="F203" s="32"/>
-      <x:c r="G203" s="32"/>
+      <x:c r="G203" s="53"/>
+      <x:c r="H203"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="31"/>
@@ -2327,7 +2549,8 @@
       <x:c r="D204" s="32"/>
       <x:c r="E204" s="32"/>
       <x:c r="F204" s="32"/>
-      <x:c r="G204" s="32"/>
+      <x:c r="G204" s="53"/>
+      <x:c r="H204"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="31"/>
@@ -2336,7 +2559,8 @@
       <x:c r="D205" s="32"/>
       <x:c r="E205" s="32"/>
       <x:c r="F205" s="32"/>
-      <x:c r="G205" s="32"/>
+      <x:c r="G205" s="53"/>
+      <x:c r="H205"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="31"/>
@@ -2345,7 +2569,8 @@
       <x:c r="D206" s="32"/>
       <x:c r="E206" s="32"/>
       <x:c r="F206" s="32"/>
-      <x:c r="G206" s="32"/>
+      <x:c r="G206" s="53"/>
+      <x:c r="H206"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="31"/>
@@ -2354,7 +2579,8 @@
       <x:c r="D207" s="32"/>
       <x:c r="E207" s="32"/>
       <x:c r="F207" s="32"/>
-      <x:c r="G207" s="32"/>
+      <x:c r="G207" s="53"/>
+      <x:c r="H207"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="31"/>
@@ -4995,17 +5221,21 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="B5:B500">
       <x:formula1>"支出,收入"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="G5:G207">
+      <x:formula1>1</x:formula1>
+      <x:formula2>120</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc082e822459948fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra034e0739def4df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5123,35 +5353,56 @@
         <x:v>文本</x:v>
       </x:c>
       <x:c r="D9" s="41" t="str">
-        <x:v>例如日常餐饮、交通出行、工资收入</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>例如日常餐饮、游戏消费、订阅消费、工资收入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="42" t="str">
+        <x:v>订阅月数</x:v>
+      </x:c>
+      <x:c r="B10" s="42" t="str">
+        <x:v>订阅消费必填</x:v>
+      </x:c>
+      <x:c r="C10" s="42" t="str">
+        <x:v>1–120 的整数</x:v>
+      </x:c>
+      <x:c r="D10" s="42" t="str">
+        <x:v>价格覆盖几个月，例如年度会员填 12；非订阅可留空或填 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
         <x:v>备注</x:v>
       </x:c>
-      <x:c r="B10" s="42" t="str">
+      <x:c r="B11" t="str">
         <x:v>选填</x:v>
       </x:c>
-      <x:c r="C10" s="42" t="str">
+      <x:c r="C11" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="D10" s="42" t="str">
+      <x:c r="D11" t="str">
         <x:v>其他需要保留的信息</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="38" customHeight="1">
-      <x:c r="A12" s="50" t="str">
-        <x:v>微信/支付宝官方账单也可以直接导入，不需要转换成此模板。本模板主要用于手动整理或其他来源账单。</x:v>
-      </x:c>
-      <x:c r="B12" s="50"/>
-      <x:c r="C12" s="50"/>
-      <x:c r="D12" s="50"/>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="54" t="str">
+        <x:v>微信/支付宝官方账单也可以直接导入，不需要转换成此模板。本模板主要用于手动整理或其他来源账单；订阅消费建议归类为“订阅消费”并填写覆盖月数。</x:v>
+      </x:c>
+      <x:c r="B13" s="54"/>
+      <x:c r="C13" s="54"/>
+      <x:c r="D13" s="54"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
     <x:mergeCell ref="A12:D12"/>
+    <x:mergeCell ref="A13:D13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
